--- a/data/清远/OTA对账/飞猪rezen.xlsx
+++ b/data/清远/OTA对账/飞猪rezen.xlsx
@@ -1,40 +1,522 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="25600" windowHeight="12200"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="飞猪re'zen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="飞猪re'zen" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+  <si>
+    <t>账单号</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>日期</t>
+  </si>
+  <si>
+    <t>结账时间</t>
+  </si>
+  <si>
+    <t>房号</t>
+  </si>
+  <si>
+    <t>外部订单号</t>
+  </si>
+  <si>
+    <t>姓名/描述</t>
+  </si>
+  <si>
+    <t>金额</t>
+  </si>
+  <si>
+    <t>借方</t>
+  </si>
+  <si>
+    <t>贷方</t>
+  </si>
+  <si>
+    <t>已核销</t>
+  </si>
+  <si>
+    <t>余额</t>
+  </si>
+  <si>
+    <t>争议余额</t>
+  </si>
+  <si>
+    <t>结账单号</t>
+  </si>
+  <si>
+    <t>订单号</t>
+  </si>
+  <si>
+    <t>财务备注</t>
+  </si>
+  <si>
+    <t>中央订单号</t>
+  </si>
+  <si>
+    <t>转账注释</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>协议单位</t>
+  </si>
+  <si>
+    <t>订单备注</t>
+  </si>
+  <si>
+    <t>入账操作员</t>
+  </si>
+  <si>
+    <t>佣金</t>
+  </si>
+  <si>
+    <t>结算价</t>
+  </si>
+  <si>
+    <t>提现额</t>
+  </si>
+  <si>
+    <t>差异</t>
+  </si>
+  <si>
+    <t>5124498696481006746</t>
+  </si>
+  <si>
+    <t>3312215366812318878</t>
+  </si>
+  <si>
+    <t>5124371006438013443</t>
+  </si>
+  <si>
+    <t>3312152006548001476</t>
+  </si>
+  <si>
+    <t>5124283131394003609</t>
+  </si>
+  <si>
+    <t>3312222999039016781</t>
+  </si>
+  <si>
+    <t>5123940482482043301</t>
+  </si>
+  <si>
+    <t>5124554496267004208</t>
+  </si>
+  <si>
+    <t>5124525048350007230</t>
+  </si>
+  <si>
+    <t>3312409586635026490</t>
+  </si>
+  <si>
+    <t>5125084921721045410</t>
+  </si>
+  <si>
+    <t>5124386486050133035</t>
+  </si>
+  <si>
+    <t>3312177098783174850</t>
+  </si>
+  <si>
+    <t>3312864590093014877</t>
+  </si>
+  <si>
+    <t>3313287445818014492</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
+  <fills count="33">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,85 +524,313 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -403,485 +1113,400 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AF16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col width="21.625" customWidth="1" min="6" max="6"/>
+    <col min="6" max="6" width="21.6272727272727" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>账单号</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>类型</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>日期</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>结账时间</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>房号</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>外部订单号</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>姓名/描述</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>金额</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>借方</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>贷方</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>已核销</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>余额</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>争议余额</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>结账单号</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>订单号</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>财务备注</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>中央订单号</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>转账注释</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>备注</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>协议单位</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>订单备注</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>入账操作员</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>佣金</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>结算价</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>提现额</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>差异</t>
-        </is>
+    <row r="1" ht="20.25" customHeight="1" spans="1:32">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="2">
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>5124498696481006746</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
+    <row r="2" spans="1:32">
+      <c r="F2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2">
         <v>2554</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AC2">
         <v>526.12</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AD2">
         <v>2554</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AE2">
         <v>2027.88</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AF2">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>3312215366812318878</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
+    <row r="3" spans="1:32">
+      <c r="F3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H3">
         <v>1265</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AC3">
         <v>134.1</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AD3">
         <v>1265</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AE3">
         <v>1130.9</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AF3">
         <v>0</v>
       </c>
     </row>
-    <row r="4">
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>5124371006438013443</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
+    <row r="4" spans="1:32">
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4">
         <v>1131</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AC4">
         <v>176.45</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AD4">
         <v>1131</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AE4">
         <v>954.55</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AF4">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>3312152006548001476</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
+    <row r="5" spans="1:32">
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H5">
         <v>1130</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AC5">
         <v>232.78</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AD5">
         <v>1130</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AE5">
         <v>897.22</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AF5">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>5124283131394003609</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
+    <row r="6" spans="1:32">
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6">
         <v>2000</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AC6">
         <v>412</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AD6">
         <v>2000</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AE6">
         <v>1588</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AF6">
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>3312222999039016781</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
+    <row r="7" spans="1:32">
+      <c r="F7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7">
         <v>2978</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AC7">
         <v>464.57</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AD7">
         <v>2978</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AE7">
         <v>2513.43</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AF7">
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>5123940482482043301</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
+    <row r="8" spans="1:32">
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8">
         <v>1517</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AC8">
         <v>312.51</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AD8">
         <v>1517</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AE8">
         <v>1204.49</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AF8">
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>5124554496267004208</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
+    <row r="9" spans="1:32">
+      <c r="F9" t="s">
+        <v>33</v>
+      </c>
+      <c r="H9">
         <v>1303</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AC9">
         <v>203.28</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AD9">
         <v>1303</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AE9">
         <v>1099.72</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AF9">
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>5124525048350007230</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
+    <row r="10" spans="1:32">
+      <c r="F10" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10">
         <v>1302</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AC10">
         <v>268.21</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AD10">
         <v>1302</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AE10">
         <v>1033.79</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AF10">
         <v>0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>3312409586635026490</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
+    <row r="11" spans="1:32">
+      <c r="F11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11">
         <v>1302</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AC11">
         <v>268.21</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AD11">
         <v>1302</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AE11">
         <v>1033.79</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AF11">
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>5125084921721045410</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
+    <row r="12" spans="1:32">
+      <c r="F12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12">
         <v>1199</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AC12">
         <v>247</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AD12">
         <v>1199</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AE12">
         <v>952</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AF12">
         <v>0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>5124386486050133035</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
+    <row r="13" spans="1:32">
+      <c r="F13" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13">
         <v>1198</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AC13">
         <v>246.79</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AD13">
         <v>1198</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AE13">
         <v>951.21</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AF13">
         <v>0</v>
       </c>
     </row>
-    <row r="14">
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>3312177098783174850</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
+    <row r="14" spans="1:32">
+      <c r="F14" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14">
         <v>1000</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AC14">
         <v>206</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AD14">
         <v>1000</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AE14">
         <v>794</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AF14">
         <v>0</v>
       </c>
     </row>
-    <row r="15">
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>3312864590093014877</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
+    <row r="15" spans="1:32">
+      <c r="F15" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15">
         <v>1488</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AC15">
         <v>306.53</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AD15">
         <v>1488</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AE15">
         <v>1181.47</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AF15">
         <v>0</v>
       </c>
     </row>
-    <row r="16">
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>3313287445818014492</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
+    <row r="16" spans="1:32">
+      <c r="F16" t="s">
+        <v>40</v>
+      </c>
+      <c r="H16">
         <v>1000</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AC16">
         <v>206</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AD16">
         <v>1000</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AE16">
         <v>794</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AF16">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>